--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -497,10 +497,10 @@
         <v>50</v>
       </c>
       <c r="I2" t="n">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="J2" t="n">
-        <v>5426</v>
+        <v>5429</v>
       </c>
     </row>
     <row r="3">
@@ -531,10 +531,10 @@
         <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J3" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="4">
@@ -565,10 +565,10 @@
         <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J4" t="n">
-        <v>925</v>
+        <v>928</v>
       </c>
     </row>
     <row r="5">
@@ -599,10 +599,10 @@
         <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="J5" t="n">
-        <v>1347</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="6">
@@ -667,10 +667,10 @@
         <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="J7" t="n">
-        <v>1597</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="8">
@@ -735,10 +735,10 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J9" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -819,7 +819,7 @@
         <v>146</v>
       </c>
       <c r="C12" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D12" t="n">
         <v>48</v>
@@ -837,10 +837,10 @@
         <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="J12" t="n">
-        <v>1130</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="13">
@@ -853,7 +853,7 @@
         <v>5167</v>
       </c>
       <c r="C13" t="n">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="D13" t="n">
         <v>998</v>
@@ -871,10 +871,10 @@
         <v>116</v>
       </c>
       <c r="I13" t="n">
-        <v>3316</v>
+        <v>3346</v>
       </c>
       <c r="J13" t="n">
-        <v>12801</v>
+        <v>12833</v>
       </c>
     </row>
   </sheetData>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39">
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40">
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="47">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="55">
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63">
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="71">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="72">
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="79">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="94">
@@ -3590,7 +3590,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="136">
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="139">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="147">
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="154">
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="160">
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="162">
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="168">
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="170">
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188">
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="196">
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="197">
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="202">
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212">
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="221">
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="226">
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="275">
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="280">
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="286">
@@ -6630,7 +6630,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288">
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="290">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="292">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="296">
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="297">
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="298">
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="309">
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="321">

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -489,7 +489,7 @@
         <v>3089</v>
       </c>
       <c r="C2" t="n">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D2" t="n">
         <v>355</v>
@@ -513,10 +513,10 @@
         <v>546</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>5429</v>
+        <v>5431</v>
       </c>
     </row>
     <row r="3">
@@ -593,10 +593,10 @@
         <v>107</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="5">
@@ -633,10 +633,10 @@
         <v>160</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         <v>337</v>
       </c>
       <c r="C6" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D6" t="n">
         <v>113</v>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="7">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C7" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D7" t="n">
         <v>196</v>
@@ -713,10 +713,10 @@
         <v>226</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>1604</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="8">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>93</v>
@@ -753,10 +753,10 @@
         <v>37</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -889,7 +889,7 @@
         <v>153</v>
       </c>
       <c r="C12" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D12" t="n">
         <v>94</v>
@@ -910,13 +910,13 @@
         <v>138</v>
       </c>
       <c r="J12" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L12" t="n">
-        <v>1146</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="13">
@@ -929,7 +929,7 @@
         <v>5459</v>
       </c>
       <c r="C13" t="n">
-        <v>2632</v>
+        <v>2635</v>
       </c>
       <c r="D13" t="n">
         <v>1170</v>
@@ -950,13 +950,13 @@
         <v>1055</v>
       </c>
       <c r="J13" t="n">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="K13" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="L13" t="n">
-        <v>12836</v>
+        <v>12851</v>
       </c>
     </row>
   </sheetData>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="78">
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80">
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="87">
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="116">
@@ -3712,7 +3712,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="138">
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="158">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="161">
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="163">
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="192">
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="200">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="201">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="226">
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="246">
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="321">
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="325">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="340">
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="346">
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="352">
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="353">
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="361">
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="371">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="399">

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -486,13 +486,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3089</v>
+        <v>3090</v>
       </c>
       <c r="C2" t="n">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D2" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E2" t="n">
         <v>102</v>
@@ -513,10 +513,10 @@
         <v>546</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>5431</v>
+        <v>5437</v>
       </c>
     </row>
     <row r="3">
@@ -529,7 +529,7 @@
         <v>286</v>
       </c>
       <c r="C3" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D3" t="n">
         <v>68</v>
@@ -547,16 +547,16 @@
         <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" t="n">
         <v>78</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="4">
@@ -566,13 +566,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C4" t="n">
         <v>208</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" t="n">
         <v>22</v>
@@ -593,7 +593,7 @@
         <v>107</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
         <v>929</v>
@@ -609,10 +609,10 @@
         <v>484</v>
       </c>
       <c r="C5" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E5" t="n">
         <v>40</v>
@@ -627,16 +627,16 @@
         <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J5" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K5" t="n">
         <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>1351</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="6">
@@ -670,13 +670,13 @@
         <v>100</v>
       </c>
       <c r="J6" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>975</v>
+        <v>977</v>
       </c>
     </row>
     <row r="7">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C7" t="n">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
         <v>196</v>
@@ -713,10 +713,10 @@
         <v>226</v>
       </c>
       <c r="K7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L7" t="n">
-        <v>1609</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="8">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D8" t="n">
         <v>30</v>
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
@@ -849,7 +849,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -886,13 +886,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C12" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E12" t="n">
         <v>22</v>
@@ -913,10 +913,10 @@
         <v>241</v>
       </c>
       <c r="K12" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="L12" t="n">
-        <v>1152</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="13">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5459</v>
+        <v>5461</v>
       </c>
       <c r="C13" t="n">
-        <v>2635</v>
+        <v>2637</v>
       </c>
       <c r="D13" t="n">
         <v>1170</v>
@@ -953,10 +953,10 @@
         <v>1557</v>
       </c>
       <c r="K13" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="L13" t="n">
-        <v>12851</v>
+        <v>12881</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D505"/>
+  <dimension ref="A1:D511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38">
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="48">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="55">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2997</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="57">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="67">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="78">
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="80">
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="87">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="88">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="90">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="94">
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="95">
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98">
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105">
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="106">
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="108">
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="122">
@@ -3428,11 +3428,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>312</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -3443,16 +3443,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10</v>
+        <v>312</v>
       </c>
     </row>
     <row r="125">
@@ -3468,11 +3468,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -3508,11 +3508,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
@@ -3528,11 +3528,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
@@ -3543,16 +3543,16 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130">
@@ -3568,11 +3568,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
     </row>
     <row r="131">
@@ -3588,11 +3588,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3608,11 +3608,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="133">
@@ -3628,11 +3628,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -3648,11 +3648,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="135">
@@ -3668,11 +3668,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136">
@@ -3688,11 +3688,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="137">
@@ -3708,31 +3708,31 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>108</v>
+        <v>30</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GUTSHIFT</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>106</v>
       </c>
     </row>
     <row r="139">
@@ -3748,11 +3748,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -3848,11 +3848,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -3923,16 +3923,16 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -3963,16 +3963,16 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -3988,11 +3988,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -4023,16 +4023,16 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -4098,21 +4098,21 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>GUTSHIFT</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4128,11 +4128,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
     </row>
     <row r="159">
@@ -4148,11 +4148,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="160">
@@ -4168,11 +4168,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -4188,11 +4188,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="162">
@@ -4208,11 +4208,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="163">
@@ -4228,11 +4228,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="164">
@@ -4243,16 +4243,16 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="165">
@@ -4268,11 +4268,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="166">
@@ -4288,11 +4288,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
@@ -4308,11 +4308,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168">
@@ -4328,11 +4328,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
@@ -4348,11 +4348,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="171">
@@ -4388,11 +4388,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="172">
@@ -4408,11 +4408,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="173">
@@ -4428,11 +4428,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>87</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174">
@@ -4443,16 +4443,16 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>23</v>
+        <v>87</v>
       </c>
     </row>
     <row r="175">
@@ -4468,11 +4468,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="176">
@@ -4488,11 +4488,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="177">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -4548,11 +4548,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -4568,11 +4568,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181">
@@ -4588,11 +4588,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="182">
@@ -4608,11 +4608,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183">
@@ -4623,16 +4623,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="184">
@@ -4648,11 +4648,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="185">
@@ -4668,11 +4668,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="186">
@@ -4688,11 +4688,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -4708,11 +4708,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -4728,11 +4728,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="189">
@@ -4748,11 +4748,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="190">
@@ -4768,11 +4768,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -4783,16 +4783,16 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>140</v>
+        <v>10</v>
       </c>
     </row>
     <row r="192">
@@ -4808,11 +4808,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>4</v>
+        <v>139</v>
       </c>
     </row>
     <row r="193">
@@ -4828,11 +4828,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194">
@@ -4848,11 +4848,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="195">
@@ -4868,11 +4868,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
@@ -4888,11 +4888,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="197">
@@ -4908,11 +4908,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
     </row>
     <row r="198">
@@ -4928,11 +4928,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="199">
@@ -4948,11 +4948,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="200">
@@ -4968,11 +4968,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>107</v>
+        <v>11</v>
       </c>
     </row>
     <row r="201">
@@ -4983,16 +4983,16 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
     </row>
     <row r="202">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="203">
@@ -5028,11 +5028,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -5048,11 +5048,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="205">
@@ -5068,11 +5068,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -5088,11 +5088,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207">
@@ -5108,11 +5108,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="208">
@@ -5128,11 +5128,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="209">
@@ -5148,11 +5148,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="210">
@@ -5168,11 +5168,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>86</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211">
@@ -5183,16 +5183,16 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>9</v>
+        <v>86</v>
       </c>
     </row>
     <row r="212">
@@ -5208,11 +5208,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="213">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -5248,11 +5248,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -5268,11 +5268,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216">
@@ -5283,16 +5283,16 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="217">
@@ -5308,11 +5308,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218">
@@ -5328,11 +5328,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
@@ -5348,11 +5348,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -5388,11 +5388,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
@@ -5408,11 +5408,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="223">
@@ -5428,11 +5428,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224">
@@ -5448,11 +5448,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
@@ -5463,16 +5463,16 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="226">
@@ -5488,11 +5488,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="227">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
@@ -5528,11 +5528,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="229">
@@ -5548,11 +5548,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
@@ -5568,11 +5568,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="231">
@@ -5588,11 +5588,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232">
@@ -5608,11 +5608,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="233">
@@ -5628,11 +5628,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>76</v>
+        <v>31</v>
       </c>
     </row>
     <row r="234">
@@ -5643,16 +5643,16 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -5663,16 +5663,16 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="236">
@@ -5688,11 +5688,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237">
@@ -5708,11 +5708,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
@@ -5723,16 +5723,16 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -5743,16 +5743,16 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="240">
@@ -5768,11 +5768,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="241">
@@ -5788,11 +5788,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="242">
@@ -5808,11 +5808,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -5828,11 +5828,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="244">
@@ -5848,11 +5848,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="245">
@@ -5868,11 +5868,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="246">
@@ -5888,51 +5888,51 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="249">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -6028,11 +6028,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="256">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -6103,16 +6103,16 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="258">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -6148,11 +6148,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -6188,11 +6188,11 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262">
@@ -6203,16 +6203,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -6223,16 +6223,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264">
@@ -6248,11 +6248,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="265">
@@ -6268,11 +6268,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
@@ -6288,11 +6288,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="267">
@@ -6308,11 +6308,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
@@ -6328,11 +6328,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
@@ -6348,11 +6348,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="270">
@@ -6363,16 +6363,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="271">
@@ -6383,16 +6383,16 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="272">
@@ -6408,11 +6408,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -6448,11 +6448,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -6463,16 +6463,16 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
@@ -6483,16 +6483,16 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
@@ -6508,11 +6508,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278">
@@ -6528,11 +6528,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
@@ -6543,16 +6543,16 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
@@ -6563,16 +6563,16 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -6588,11 +6588,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="282">
@@ -6608,11 +6608,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
@@ -6623,16 +6623,16 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
@@ -6643,16 +6643,16 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="285">
@@ -6668,11 +6668,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286">
@@ -6688,11 +6688,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
@@ -6703,16 +6703,16 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288">
@@ -6723,16 +6723,16 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="289">
@@ -6748,11 +6748,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="290">
@@ -6768,11 +6768,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
@@ -6788,11 +6788,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
@@ -6808,47 +6808,47 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>325</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -6868,11 +6868,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>74</v>
+        <v>325</v>
       </c>
     </row>
     <row r="296">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="297">
@@ -6908,11 +6908,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>13</v>
+        <v>74</v>
       </c>
     </row>
     <row r="298">
@@ -6928,11 +6928,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
@@ -6948,11 +6948,11 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>160</v>
+        <v>13</v>
       </c>
     </row>
     <row r="300">
@@ -6968,11 +6968,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="301">
@@ -6988,11 +6988,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>39</v>
+        <v>160</v>
       </c>
     </row>
     <row r="302">
@@ -7003,16 +7003,16 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="303">
@@ -7023,16 +7023,16 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="304">
@@ -7048,11 +7048,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="305">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D305" t="n">
@@ -7088,11 +7088,11 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
@@ -7108,11 +7108,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D308" t="n">
@@ -7143,16 +7143,16 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="310">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="311">
@@ -7183,16 +7183,16 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -7223,12 +7223,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D313" t="n">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -7263,27 +7263,27 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7292,27 +7292,27 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D318" t="n">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D320" t="n">
@@ -7388,11 +7388,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322">
@@ -7408,11 +7408,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="323">
@@ -7428,11 +7428,11 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="324">
@@ -7443,16 +7443,16 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="325">
@@ -7463,16 +7463,16 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="326">
@@ -7488,11 +7488,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="327">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D327" t="n">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D328" t="n">
@@ -7548,11 +7548,11 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -7568,11 +7568,11 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -7583,16 +7583,16 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="332">
@@ -7603,16 +7603,16 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="333">
@@ -7628,11 +7628,11 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="334">
@@ -7648,11 +7648,11 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="335">
@@ -7668,11 +7668,11 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -7688,11 +7688,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -7708,11 +7708,11 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="338">
@@ -7728,11 +7728,11 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="339">
@@ -7743,16 +7743,16 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="340">
@@ -7763,16 +7763,16 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="341">
@@ -7788,11 +7788,11 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="342">
@@ -7808,11 +7808,11 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -7828,11 +7828,11 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -7848,11 +7848,11 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -7863,16 +7863,16 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
@@ -7883,16 +7883,16 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
@@ -7908,11 +7908,11 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="348">
@@ -7928,11 +7928,11 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="349">
@@ -7948,11 +7948,11 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="350">
@@ -7968,11 +7968,11 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="351">
@@ -7988,11 +7988,11 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="352">
@@ -8008,11 +8008,11 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="353">
@@ -8023,16 +8023,16 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="354">
@@ -8043,16 +8043,16 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="355">
@@ -8068,11 +8068,11 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="356">
@@ -8088,11 +8088,11 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="357">
@@ -8108,11 +8108,11 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -8128,11 +8128,11 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359">
@@ -8148,11 +8148,11 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="360">
@@ -8168,11 +8168,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="361">
@@ -8188,11 +8188,11 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="362">
@@ -8203,16 +8203,16 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="363">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="364">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -8252,7 +8252,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -8263,16 +8263,16 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -8288,11 +8288,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -8308,11 +8308,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="368">
@@ -8328,11 +8328,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369">
@@ -8348,11 +8348,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="370">
@@ -8363,16 +8363,16 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371">
@@ -8383,16 +8383,16 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="372">
@@ -8408,11 +8408,11 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="373">
@@ -8428,11 +8428,11 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374">
@@ -8448,11 +8448,11 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="375">
@@ -8468,11 +8468,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="376">
@@ -8488,11 +8488,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
@@ -8508,11 +8508,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -8528,11 +8528,11 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="379">
@@ -8543,16 +8543,16 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="380">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -8583,16 +8583,16 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="382">
@@ -8603,16 +8603,16 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -8623,16 +8623,16 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -8648,11 +8648,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="385">
@@ -8668,71 +8668,71 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="389">
@@ -8748,11 +8748,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="390">
@@ -8768,11 +8768,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="391">
@@ -8788,11 +8788,11 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392">
@@ -8808,11 +8808,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="393">
@@ -8823,16 +8823,16 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394">
@@ -8843,16 +8843,16 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D395" t="n">
@@ -8883,16 +8883,16 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="397">
@@ -8903,16 +8903,16 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -8923,16 +8923,16 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="399">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D400" t="n">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -9012,7 +9012,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="403">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="404">
@@ -9043,12 +9043,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D404" t="n">
@@ -9063,16 +9063,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="406">
@@ -9088,11 +9088,11 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="407">
@@ -9108,11 +9108,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="408">
@@ -9128,11 +9128,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -9148,11 +9148,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -9183,16 +9183,16 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="412">
@@ -9203,16 +9203,16 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="413">
@@ -9223,16 +9223,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="415">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -9283,16 +9283,16 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -9303,16 +9303,16 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -9323,16 +9323,16 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="419">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D419" t="n">
@@ -9363,16 +9363,16 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -9383,16 +9383,16 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="422">
@@ -9408,11 +9408,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="423">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D423" t="n">
@@ -9443,16 +9443,16 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="425">
@@ -9463,16 +9463,16 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="426">
@@ -9483,16 +9483,16 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="427">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D427" t="n">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D428" t="n">
@@ -9543,16 +9543,16 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="430">
@@ -9568,11 +9568,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="431">
@@ -9588,11 +9588,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="432">
@@ -9608,111 +9608,111 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="438">
@@ -9723,16 +9723,16 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="439">
@@ -9743,16 +9743,16 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="440">
@@ -9763,16 +9763,16 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="441">
@@ -9788,11 +9788,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="442">
@@ -9808,11 +9808,11 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="443">
@@ -9828,11 +9828,11 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>116</v>
+        <v>1</v>
       </c>
     </row>
     <row r="444">
@@ -9843,16 +9843,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="445">
@@ -9863,16 +9863,16 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="446">
@@ -9883,16 +9883,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="447">
@@ -9903,16 +9903,16 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="448">
@@ -9923,16 +9923,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>7</v>
+        <v>116</v>
       </c>
     </row>
     <row r="449">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D449" t="n">
@@ -9968,11 +9968,11 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
@@ -9983,16 +9983,16 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="452">
@@ -10003,16 +10003,16 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
@@ -10023,16 +10023,16 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="454">
@@ -10043,16 +10043,16 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="455">
@@ -10063,16 +10063,16 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="456">
@@ -10088,11 +10088,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="457">
@@ -10108,11 +10108,11 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="458">
@@ -10123,16 +10123,16 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="459">
@@ -10143,16 +10143,16 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="460">
@@ -10163,16 +10163,16 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="461">
@@ -10183,16 +10183,16 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="462">
@@ -10203,16 +10203,16 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="463">
@@ -10228,11 +10228,11 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="464">
@@ -10248,11 +10248,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
@@ -10268,11 +10268,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="466">
@@ -10288,11 +10288,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="467">
@@ -10303,16 +10303,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="468">
@@ -10323,16 +10323,16 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="469">
@@ -10343,16 +10343,16 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="470">
@@ -10363,16 +10363,16 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="471">
@@ -10383,16 +10383,16 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="472">
@@ -10408,11 +10408,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="473">
@@ -10428,11 +10428,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474">
@@ -10448,11 +10448,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="475">
@@ -10463,16 +10463,16 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="476">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D476" t="n">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="478">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="479">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -10552,7 +10552,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="480">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
@@ -10603,16 +10603,16 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="483">
@@ -10623,12 +10623,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D483" t="n">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -10668,11 +10668,11 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="486">
@@ -10688,11 +10688,11 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="487">
@@ -10703,16 +10703,16 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488">
@@ -10723,16 +10723,16 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="489">
@@ -10743,16 +10743,16 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="490">
@@ -10763,16 +10763,16 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -10783,16 +10783,16 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="492">
@@ -10808,11 +10808,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="493">
@@ -10828,11 +10828,11 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -10848,11 +10848,11 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="495">
@@ -10863,16 +10863,16 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="496">
@@ -10883,16 +10883,16 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -10903,16 +10903,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="498">
@@ -10923,16 +10923,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="499">
@@ -10943,16 +10943,16 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="500">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D500" t="n">
@@ -10983,16 +10983,16 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -11003,16 +11003,16 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -11023,16 +11023,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="504">
@@ -11048,11 +11048,11 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="505">
@@ -11068,10 +11068,130 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
+          <t>Faceless</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D505" t="n">
+      <c r="D511" t="n">
         <v>11</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -673,10 +673,10 @@
         <v>112</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="7">
@@ -889,7 +889,7 @@
         <v>155</v>
       </c>
       <c r="C12" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -913,10 +913,10 @@
         <v>241</v>
       </c>
       <c r="K12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L12" t="n">
-        <v>1165</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="13">
@@ -929,7 +929,7 @@
         <v>5461</v>
       </c>
       <c r="C13" t="n">
-        <v>2637</v>
+        <v>2639</v>
       </c>
       <c r="D13" t="n">
         <v>1170</v>
@@ -953,10 +953,10 @@
         <v>1557</v>
       </c>
       <c r="K13" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="L13" t="n">
-        <v>12881</v>
+        <v>12888</v>
       </c>
     </row>
   </sheetData>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="159">
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="164">
@@ -4652,7 +4652,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="185">
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="227">
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="340">
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="348">
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="373">

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -486,19 +486,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3090</v>
+        <v>3111</v>
       </c>
       <c r="C2" t="n">
-        <v>705</v>
+        <v>761</v>
       </c>
       <c r="D2" t="n">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F2" t="n">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="G2" t="n">
         <v>35</v>
@@ -507,16 +507,16 @@
         <v>54</v>
       </c>
       <c r="I2" t="n">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="J2" t="n">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>5437</v>
+        <v>5547</v>
       </c>
     </row>
     <row r="3">
@@ -526,13 +526,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C3" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E3" t="n">
         <v>16</v>
@@ -547,16 +547,16 @@
         <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J3" t="n">
         <v>78</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>663</v>
+        <v>670</v>
       </c>
     </row>
     <row r="4">
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C4" t="n">
         <v>208</v>
       </c>
       <c r="D4" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
         <v>4</v>
@@ -587,16 +587,16 @@
         <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K4" t="n">
         <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>929</v>
+        <v>939</v>
       </c>
     </row>
     <row r="5">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="C5" t="n">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D5" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
         <v>33</v>
@@ -627,16 +627,16 @@
         <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J5" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>1355</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="6">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C6" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D6" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" t="n">
         <v>29</v>
-      </c>
-      <c r="F6" t="n">
-        <v>28</v>
       </c>
       <c r="G6" t="n">
         <v>8</v>
@@ -667,16 +667,16 @@
         <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J6" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>978</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="7">
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="C7" t="n">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E7" t="n">
         <v>47</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="J7" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="K7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L7" t="n">
-        <v>1611</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="8">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
         <v>13</v>
@@ -750,13 +750,13 @@
         <v>34</v>
       </c>
       <c r="J8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>347</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C9" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="C12" t="n">
-        <v>451</v>
+        <v>362</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="J12" t="n">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="K12" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="L12" t="n">
-        <v>1171</v>
+        <v>916</v>
       </c>
     </row>
     <row r="13">
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D511"/>
+  <dimension ref="A1:D506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46">
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>92</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>665</v>
+        <v>673</v>
       </c>
     </row>
     <row r="48">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="53">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="54">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="55">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2999</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="57">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60">
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="67">
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75">
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>377</v>
+        <v>387</v>
       </c>
     </row>
     <row r="78">
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="80">
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="84">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85">
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>449</v>
+        <v>459</v>
       </c>
     </row>
     <row r="87">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="88">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="90">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="94">
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="95">
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96">
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="97">
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106">
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="113">
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="115">
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="116">
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="118">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="120">
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121">
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="122">
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="123">
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="125">
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="131">
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137">
@@ -3712,7 +3712,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="138">
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="139">
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="159">
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="160">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="162">
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163">
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="164">
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="166">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="171">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173">
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174">
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="182">
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="184">
@@ -4652,7 +4652,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="185">
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="193">
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="195">
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="199">
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="202">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="203">
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="205">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="209">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="210">
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="212">
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="218">
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="224">
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225">
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="227">
@@ -5612,7 +5612,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="233">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="234">
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="235">
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="236">
@@ -5932,7 +5932,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="249">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -5963,12 +5963,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -5983,16 +5983,16 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -6023,16 +6023,16 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -6043,16 +6043,16 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255">
@@ -6063,16 +6063,16 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -6103,16 +6103,16 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="259">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="260">
@@ -6163,16 +6163,16 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261">
@@ -6183,16 +6183,16 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="262">
@@ -6203,16 +6203,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263">
@@ -6223,16 +6223,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
@@ -6248,11 +6248,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="265">
@@ -6268,11 +6268,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="266">
@@ -6288,11 +6288,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
@@ -6308,11 +6308,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="268">
@@ -6323,16 +6323,16 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269">
@@ -6343,16 +6343,16 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -6363,16 +6363,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -6383,16 +6383,16 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -6423,16 +6423,16 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="274">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="278">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -6543,16 +6543,16 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="281">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -6623,16 +6623,16 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="284">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="286">
@@ -6683,16 +6683,16 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="287">
@@ -6703,16 +6703,16 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -6748,11 +6748,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290">
@@ -6768,91 +6768,91 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>3</v>
+        <v>279</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -6868,11 +6868,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>325</v>
+        <v>12</v>
       </c>
     </row>
     <row r="296">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D296" t="n">
@@ -6908,11 +6908,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>74</v>
+        <v>152</v>
       </c>
     </row>
     <row r="298">
@@ -6928,11 +6928,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="299">
@@ -6948,11 +6948,11 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="300">
@@ -6963,16 +6963,16 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
     </row>
     <row r="301">
@@ -6983,16 +6983,16 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>160</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
@@ -7003,16 +7003,16 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
@@ -7023,16 +7023,16 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7048,11 +7048,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -7068,11 +7068,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="306">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D306" t="n">
@@ -7108,11 +7108,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="308">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D308" t="n">
@@ -7143,16 +7143,16 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D312" t="n">
@@ -7223,16 +7223,16 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -7248,11 +7248,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
@@ -7263,12 +7263,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D315" t="n">
@@ -7288,27 +7288,27 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D317" t="n">
@@ -7328,11 +7328,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D319" t="n">
@@ -7368,11 +7368,11 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
@@ -7388,11 +7388,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="322">
@@ -7403,16 +7403,16 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="323">
@@ -7423,16 +7423,16 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="324">
@@ -7443,16 +7443,16 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325">
@@ -7463,16 +7463,16 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="326">
@@ -7488,11 +7488,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -7508,11 +7508,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="328">
@@ -7528,11 +7528,11 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="329">
@@ -7543,16 +7543,16 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="330">
@@ -7563,16 +7563,16 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="331">
@@ -7583,16 +7583,16 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -7603,16 +7603,16 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -7628,11 +7628,11 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -7648,11 +7648,11 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="335">
@@ -7668,11 +7668,11 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -7688,11 +7688,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="337">
@@ -7703,16 +7703,16 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="338">
@@ -7723,16 +7723,16 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
@@ -7743,16 +7743,16 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="340">
@@ -7763,16 +7763,16 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
@@ -7788,11 +7788,11 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D342" t="n">
@@ -7823,16 +7823,16 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="344">
@@ -7843,16 +7843,16 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -7863,16 +7863,16 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="346">
@@ -7883,16 +7883,16 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="347">
@@ -7908,11 +7908,11 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="348">
@@ -7928,11 +7928,11 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="349">
@@ -7948,11 +7948,11 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="350">
@@ -7968,11 +7968,11 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="351">
@@ -7988,11 +7988,11 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="352">
@@ -8003,16 +8003,16 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="353">
@@ -8023,16 +8023,16 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="354">
@@ -8043,16 +8043,16 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -8068,11 +8068,11 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -8088,11 +8088,11 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="357">
@@ -8108,11 +8108,11 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="358">
@@ -8128,11 +8128,11 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="359">
@@ -8148,11 +8148,11 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="360">
@@ -8168,11 +8168,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="361">
@@ -8183,16 +8183,16 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="362">
@@ -8203,16 +8203,16 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
@@ -8223,16 +8223,16 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="364">
@@ -8243,16 +8243,16 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -8288,11 +8288,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D367" t="n">
@@ -8328,11 +8328,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369">
@@ -8348,11 +8348,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="370">
@@ -8363,16 +8363,16 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="371">
@@ -8383,16 +8383,16 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372">
@@ -8408,11 +8408,11 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="373">
@@ -8428,11 +8428,11 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="374">
@@ -8448,11 +8448,11 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="375">
@@ -8468,11 +8468,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -8488,11 +8488,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="377">
@@ -8508,11 +8508,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="378">
@@ -8528,11 +8528,11 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -8548,11 +8548,11 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="380">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -8592,7 +8592,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="383">
@@ -8623,16 +8623,16 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
@@ -8648,11 +8648,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385">
@@ -8668,11 +8668,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -8688,51 +8688,51 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="389">
@@ -8748,11 +8748,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D391" t="n">
@@ -8803,12 +8803,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D392" t="n">
@@ -8823,16 +8823,16 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="394">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D394" t="n">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D395" t="n">
@@ -8883,16 +8883,16 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D397" t="n">
@@ -8923,16 +8923,16 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="399">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D400" t="n">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="402">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -9012,7 +9012,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="403">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="404">
@@ -9043,12 +9043,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D404" t="n">
@@ -9063,16 +9063,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="406">
@@ -9088,11 +9088,11 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="407">
@@ -9108,11 +9108,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="408">
@@ -9128,11 +9128,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="409">
@@ -9148,11 +9148,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="411">
@@ -9183,16 +9183,16 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -9203,16 +9203,16 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -9223,16 +9223,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="415">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -9283,16 +9283,16 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
@@ -9303,16 +9303,16 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="418">
@@ -9323,16 +9323,16 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="419">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D419" t="n">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D420" t="n">
@@ -9383,16 +9383,16 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422">
@@ -9408,11 +9408,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D423" t="n">
@@ -9448,11 +9448,11 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="425">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D425" t="n">
@@ -9483,16 +9483,16 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427">
@@ -9508,11 +9508,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -9523,16 +9523,16 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="429">
@@ -9543,16 +9543,16 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="430">
@@ -9568,11 +9568,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -9588,11 +9588,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -9608,11 +9608,11 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -9628,11 +9628,11 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="434">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D434" t="n">
@@ -9668,51 +9668,51 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="438">
@@ -9723,16 +9723,16 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439">
@@ -9743,16 +9743,16 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="440">
@@ -9763,16 +9763,16 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="441">
@@ -9788,11 +9788,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="442">
@@ -9808,11 +9808,11 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="443">
@@ -9828,11 +9828,11 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
     </row>
     <row r="444">
@@ -9843,16 +9843,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="445">
@@ -9863,16 +9863,16 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446">
@@ -9883,16 +9883,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="447">
@@ -9903,16 +9903,16 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448">
@@ -9923,16 +9923,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>116</v>
+        <v>7</v>
       </c>
     </row>
     <row r="449">
@@ -9948,11 +9948,11 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="450">
@@ -9968,11 +9968,11 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="451">
@@ -9983,16 +9983,16 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="452">
@@ -10003,16 +10003,16 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="453">
@@ -10023,16 +10023,16 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -10043,16 +10043,16 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -10063,16 +10063,16 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="456">
@@ -10088,11 +10088,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="457">
@@ -10108,11 +10108,11 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="458">
@@ -10123,16 +10123,16 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="459">
@@ -10143,16 +10143,16 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -10163,16 +10163,16 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="461">
@@ -10183,16 +10183,16 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="462">
@@ -10203,16 +10203,16 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="463">
@@ -10228,11 +10228,11 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="464">
@@ -10248,11 +10248,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="465">
@@ -10268,11 +10268,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="466">
@@ -10288,11 +10288,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="467">
@@ -10303,16 +10303,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="468">
@@ -10323,16 +10323,16 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469">
@@ -10343,16 +10343,16 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="470">
@@ -10363,16 +10363,16 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="471">
@@ -10383,16 +10383,16 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="472">
@@ -10408,11 +10408,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="473">
@@ -10428,11 +10428,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="474">
@@ -10448,11 +10448,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="475">
@@ -10463,16 +10463,16 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D476" t="n">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="478">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -10552,7 +10552,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="480">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="481">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="482">
@@ -10603,16 +10603,16 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483">
@@ -10623,12 +10623,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D483" t="n">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -10668,11 +10668,11 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="486">
@@ -10688,11 +10688,11 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="487">
@@ -10703,16 +10703,16 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="488">
@@ -10723,16 +10723,16 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="489">
@@ -10743,12 +10743,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D489" t="n">
@@ -10763,16 +10763,16 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -10783,16 +10783,16 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -10808,11 +10808,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="493">
@@ -10828,11 +10828,11 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="494">
@@ -10848,11 +10848,11 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="495">
@@ -10863,16 +10863,16 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496">
@@ -10883,12 +10883,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D496" t="n">
@@ -10903,16 +10903,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="498">
@@ -10923,16 +10923,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="499">
@@ -10943,16 +10943,16 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="500">
@@ -10963,16 +10963,16 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -10983,16 +10983,16 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D502" t="n">
@@ -11023,16 +11023,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="504">
@@ -11048,11 +11048,11 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="505">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D505" t="n">
@@ -11088,110 +11088,10 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>Middle Eastern/Arab</t>
-        </is>
-      </c>
-      <c r="D507" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>Mixed/Ambiguous</t>
-        </is>
-      </c>
-      <c r="D508" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="D509" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>South Asian</t>
-        </is>
-      </c>
-      <c r="D510" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>White/European</t>
-        </is>
-      </c>
-      <c r="D511" t="n">
         <v>11</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -489,7 +489,7 @@
         <v>3111</v>
       </c>
       <c r="C2" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D2" t="n">
         <v>361</v>
@@ -516,7 +516,7 @@
         <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>5547</v>
+        <v>5548</v>
       </c>
     </row>
     <row r="3">
@@ -633,10 +633,10 @@
         <v>165</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="6">
@@ -889,13 +889,13 @@
         <v>89</v>
       </c>
       <c r="C12" t="n">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
         <v>9</v>
@@ -904,7 +904,7 @@
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
         <v>117</v>
@@ -913,10 +913,10 @@
         <v>205</v>
       </c>
       <c r="K12" t="n">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="L12" t="n">
-        <v>916</v>
+        <v>994</v>
       </c>
     </row>
     <row r="13">
@@ -929,13 +929,13 @@
         <v>5461</v>
       </c>
       <c r="C13" t="n">
-        <v>2639</v>
+        <v>2644</v>
       </c>
       <c r="D13" t="n">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="E13" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F13" t="n">
         <v>422</v>
@@ -944,7 +944,7 @@
         <v>67</v>
       </c>
       <c r="H13" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I13" t="n">
         <v>1055</v>
@@ -953,10 +953,10 @@
         <v>1557</v>
       </c>
       <c r="K13" t="n">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="L13" t="n">
-        <v>12888</v>
+        <v>12968</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D506"/>
+  <dimension ref="A1:D514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="78">
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="95">
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="133">
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="159">
@@ -4168,11 +4168,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -4188,11 +4188,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -4208,11 +4208,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163">
@@ -4228,11 +4228,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164">
@@ -4248,11 +4248,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>9</v>
+        <v>75</v>
       </c>
     </row>
     <row r="165">
@@ -4263,16 +4263,16 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166">
@@ -4288,11 +4288,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="167">
@@ -4308,11 +4308,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
@@ -4328,11 +4328,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169">
@@ -4348,11 +4348,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171">
@@ -4388,11 +4388,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172">
@@ -4408,11 +4408,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="173">
@@ -4428,11 +4428,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="174">
@@ -4448,11 +4448,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>87</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175">
@@ -4463,16 +4463,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>23</v>
+        <v>87</v>
       </c>
     </row>
     <row r="176">
@@ -4488,11 +4488,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="177">
@@ -4508,11 +4508,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -4568,11 +4568,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -4588,11 +4588,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="182">
@@ -4608,11 +4608,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="183">
@@ -4628,11 +4628,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184">
@@ -4643,16 +4643,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="185">
@@ -4668,11 +4668,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="186">
@@ -4688,11 +4688,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187">
@@ -4708,11 +4708,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -4728,11 +4728,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -4748,11 +4748,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190">
@@ -4768,11 +4768,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="191">
@@ -4788,11 +4788,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -4803,16 +4803,16 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>144</v>
+        <v>10</v>
       </c>
     </row>
     <row r="193">
@@ -4828,11 +4828,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>4</v>
+        <v>148</v>
       </c>
     </row>
     <row r="194">
@@ -4848,11 +4848,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
     </row>
     <row r="195">
@@ -4868,11 +4868,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="196">
@@ -4888,11 +4888,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -4908,11 +4908,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="198">
@@ -4928,11 +4928,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>66</v>
+        <v>14</v>
       </c>
     </row>
     <row r="199">
@@ -4948,11 +4948,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="200">
@@ -4968,11 +4968,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="201">
@@ -4988,11 +4988,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>114</v>
+        <v>11</v>
       </c>
     </row>
     <row r="202">
@@ -5003,16 +5003,16 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>66</v>
+        <v>115</v>
       </c>
     </row>
     <row r="203">
@@ -5028,11 +5028,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
     </row>
     <row r="204">
@@ -5048,11 +5048,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -5068,11 +5068,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="206">
@@ -5088,11 +5088,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -5108,11 +5108,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208">
@@ -5128,11 +5128,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="209">
@@ -5148,11 +5148,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="210">
@@ -5168,11 +5168,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="211">
@@ -5188,11 +5188,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212">
@@ -5203,16 +5203,16 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="213">
@@ -5228,11 +5228,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="214">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -5303,16 +5303,16 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="218">
@@ -5328,11 +5328,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="219">
@@ -5348,11 +5348,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
@@ -5368,11 +5368,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="221">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -5408,11 +5408,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -5428,11 +5428,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224">
@@ -5448,11 +5448,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="225">
@@ -5468,11 +5468,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
@@ -5483,16 +5483,16 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="227">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="228">
@@ -5528,11 +5528,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -5548,11 +5548,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="230">
@@ -5568,11 +5568,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231">
@@ -5588,11 +5588,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="232">
@@ -5608,11 +5608,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233">
@@ -5628,11 +5628,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="234">
@@ -5648,11 +5648,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="235">
@@ -5668,11 +5668,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
     </row>
     <row r="236">
@@ -5683,16 +5683,16 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="237">
@@ -5708,11 +5708,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="238">
@@ -5728,11 +5728,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
@@ -5748,11 +5748,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -5763,16 +5763,16 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="241">
@@ -5788,11 +5788,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="242">
@@ -5808,11 +5808,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="243">
@@ -5828,11 +5828,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
@@ -5848,11 +5848,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="245">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -5888,11 +5888,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="247">
@@ -5908,11 +5908,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="248">
@@ -5928,31 +5928,31 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="250">
@@ -5963,16 +5963,16 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="251">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6043,16 +6043,16 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -6063,12 +6063,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -6088,11 +6088,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -6128,11 +6128,11 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -6143,16 +6143,16 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -6163,16 +6163,16 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261">
@@ -6188,11 +6188,11 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="262">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -6228,11 +6228,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="264">
@@ -6248,11 +6248,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="265">
@@ -6268,11 +6268,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266">
@@ -6288,11 +6288,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="267">
@@ -6308,11 +6308,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="268">
@@ -6323,16 +6323,16 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
@@ -6343,16 +6343,16 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="270">
@@ -6368,11 +6368,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -6408,11 +6408,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -6423,16 +6423,16 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
@@ -6443,16 +6443,16 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
@@ -6468,11 +6468,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276">
@@ -6488,11 +6488,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
@@ -6503,16 +6503,16 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278">
@@ -6523,16 +6523,16 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -6548,11 +6548,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="280">
@@ -6568,11 +6568,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
@@ -6583,16 +6583,16 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">
@@ -6623,16 +6623,16 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="284">
@@ -6648,11 +6648,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285">
@@ -6663,16 +6663,16 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286">
@@ -6683,16 +6683,16 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287">
@@ -6703,16 +6703,16 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288">
@@ -6728,11 +6728,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="289">
@@ -6748,11 +6748,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290">
@@ -6768,71 +6768,71 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>279</v>
+        <v>4</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294">
@@ -6848,11 +6848,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1</v>
+        <v>279</v>
       </c>
     </row>
     <row r="295">
@@ -6868,11 +6868,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="296">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="297">
@@ -6908,11 +6908,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>152</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
@@ -6928,11 +6928,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="299">
@@ -6948,11 +6948,11 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300">
@@ -6963,16 +6963,16 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>65</v>
+        <v>152</v>
       </c>
     </row>
     <row r="301">
@@ -6983,16 +6983,16 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="302">
@@ -7003,16 +7003,16 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="303">
@@ -7028,11 +7028,11 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="304">
@@ -7048,11 +7048,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -7068,11 +7068,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -7088,11 +7088,11 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -7108,11 +7108,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="308">
@@ -7123,16 +7123,16 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="309">
@@ -7143,16 +7143,16 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310">
@@ -7163,16 +7163,16 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="311">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="312">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D312" t="n">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -7243,12 +7243,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D314" t="n">
@@ -7263,12 +7263,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D315" t="n">
@@ -7283,52 +7283,52 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D318" t="n">
@@ -7338,12 +7338,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="320">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D320" t="n">
@@ -7388,11 +7388,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322">
@@ -7403,16 +7403,16 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
@@ -7423,16 +7423,16 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
@@ -7443,16 +7443,16 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="325">
@@ -7463,16 +7463,16 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="326">
@@ -7488,11 +7488,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="327">
@@ -7508,11 +7508,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -7528,11 +7528,11 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -7543,16 +7543,16 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -7563,16 +7563,16 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -7583,16 +7583,16 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -7603,16 +7603,16 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="333">
@@ -7623,16 +7623,16 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="334">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D334" t="n">
@@ -7668,11 +7668,11 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="336">
@@ -7688,11 +7688,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -7703,16 +7703,16 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="338">
@@ -7723,16 +7723,16 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="339">
@@ -7743,16 +7743,16 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="340">
@@ -7763,16 +7763,16 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341">
@@ -7783,16 +7783,16 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="342">
@@ -7808,11 +7808,11 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="343">
@@ -7823,16 +7823,16 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -7843,16 +7843,16 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -7863,16 +7863,16 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
@@ -7883,16 +7883,16 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
@@ -7903,16 +7903,16 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
@@ -7928,11 +7928,11 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="349">
@@ -7948,11 +7948,11 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350">
@@ -7968,11 +7968,11 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="351">
@@ -7988,11 +7988,11 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="352">
@@ -8003,16 +8003,16 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="353">
@@ -8023,16 +8023,16 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="354">
@@ -8043,16 +8043,16 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="355">
@@ -8063,16 +8063,16 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="356">
@@ -8083,16 +8083,16 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="357">
@@ -8108,11 +8108,11 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="358">
@@ -8128,11 +8128,11 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="359">
@@ -8148,11 +8148,11 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
@@ -8168,11 +8168,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="361">
@@ -8183,16 +8183,16 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="362">
@@ -8203,16 +8203,16 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="363">
@@ -8223,16 +8223,16 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="364">
@@ -8243,16 +8243,16 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -8263,16 +8263,16 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="366">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D366" t="n">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D367" t="n">
@@ -8323,16 +8323,16 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369">
@@ -8348,11 +8348,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="370">
@@ -8363,16 +8363,16 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371">
@@ -8383,16 +8383,16 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -8403,16 +8403,16 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -8423,16 +8423,16 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -8463,16 +8463,16 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="376">
@@ -8488,11 +8488,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="377">
@@ -8508,11 +8508,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -8528,11 +8528,11 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="379">
@@ -8548,11 +8548,11 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="380">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -8583,16 +8583,16 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D382" t="n">
@@ -8623,16 +8623,16 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="384">
@@ -8643,16 +8643,16 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -8663,16 +8663,16 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="386">
@@ -8683,72 +8683,72 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D389" t="n">
@@ -8758,17 +8758,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D390" t="n">
@@ -8778,41 +8778,41 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="393">
@@ -8823,16 +8823,16 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394">
@@ -8843,16 +8843,16 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D395" t="n">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D396" t="n">
@@ -8903,16 +8903,16 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398">
@@ -8923,16 +8923,16 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="399">
@@ -8943,16 +8943,16 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="400">
@@ -8963,16 +8963,16 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="401">
@@ -8983,16 +8983,16 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="402">
@@ -9003,16 +9003,16 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="403">
@@ -9023,16 +9023,16 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="404">
@@ -9043,16 +9043,16 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="405">
@@ -9063,16 +9063,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="406">
@@ -9083,16 +9083,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407">
@@ -9103,16 +9103,16 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="408">
@@ -9123,16 +9123,16 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="409">
@@ -9148,11 +9148,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="410">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="411">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D411" t="n">
@@ -9203,12 +9203,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D412" t="n">
@@ -9223,16 +9223,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="414">
@@ -9243,16 +9243,16 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="415">
@@ -9263,16 +9263,16 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="416">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D416" t="n">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="418">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="419">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -9352,7 +9352,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -9363,16 +9363,16 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421">
@@ -9383,16 +9383,16 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="422">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D422" t="n">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D423" t="n">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="425">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="426">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D426" t="n">
@@ -9503,16 +9503,16 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -9523,16 +9523,16 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429">
@@ -9543,16 +9543,16 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="430">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D430" t="n">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D431" t="n">
@@ -9603,16 +9603,16 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="433">
@@ -9623,16 +9623,16 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -9678,12 +9678,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -9692,18 +9692,18 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -9712,18 +9712,18 @@
         </is>
       </c>
       <c r="D437" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -9738,12 +9738,12 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -9752,18 +9752,18 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -9772,18 +9772,18 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -9792,18 +9792,18 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -9812,18 +9812,18 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>116</v>
+        <v>3</v>
       </c>
     </row>
     <row r="444">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="445">
@@ -9863,16 +9863,16 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="446">
@@ -9883,16 +9883,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447">
@@ -9903,16 +9903,16 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="448">
@@ -9923,16 +9923,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="449">
@@ -9943,16 +9943,16 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="450">
@@ -9963,16 +9963,16 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="451">
@@ -9983,16 +9983,16 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>5</v>
+        <v>116</v>
       </c>
     </row>
     <row r="452">
@@ -10003,12 +10003,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D452" t="n">
@@ -10023,16 +10023,16 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -10043,16 +10043,16 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="455">
@@ -10063,16 +10063,16 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -10083,16 +10083,16 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="457">
@@ -10103,16 +10103,16 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="458">
@@ -10123,16 +10123,16 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="459">
@@ -10143,16 +10143,16 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="460">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -10172,7 +10172,7 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="461">
@@ -10183,16 +10183,16 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="462">
@@ -10203,16 +10203,16 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463">
@@ -10223,16 +10223,16 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="464">
@@ -10243,16 +10243,16 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="465">
@@ -10263,16 +10263,16 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="466">
@@ -10288,11 +10288,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="467">
@@ -10303,16 +10303,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="468">
@@ -10323,16 +10323,16 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="469">
@@ -10343,16 +10343,16 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="470">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="471">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -10392,7 +10392,7 @@
         </is>
       </c>
       <c r="D471" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="472">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -10412,7 +10412,7 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="473">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -10432,7 +10432,7 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="474">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="D474" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="475">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="476">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D476" t="n">
@@ -10503,16 +10503,16 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="478">
@@ -10523,16 +10523,16 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="479">
@@ -10543,16 +10543,16 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -10563,16 +10563,16 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="481">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D481" t="n">
@@ -10603,16 +10603,16 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="483">
@@ -10623,16 +10623,16 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="484">
@@ -10643,16 +10643,16 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D485" t="n">
@@ -10683,16 +10683,16 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="487">
@@ -10703,16 +10703,16 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="488">
@@ -10723,16 +10723,16 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="489">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -10763,16 +10763,16 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="491">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -10792,7 +10792,7 @@
         </is>
       </c>
       <c r="D491" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="492">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -10812,7 +10812,7 @@
         </is>
       </c>
       <c r="D492" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="493">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -10832,7 +10832,7 @@
         </is>
       </c>
       <c r="D493" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="495">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -10872,7 +10872,7 @@
         </is>
       </c>
       <c r="D495" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="496">
@@ -10883,12 +10883,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D496" t="n">
@@ -10903,16 +10903,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="498">
@@ -10923,16 +10923,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
@@ -10943,16 +10943,16 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -10963,16 +10963,16 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="501">
@@ -10983,16 +10983,16 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="502">
@@ -11003,16 +11003,16 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="503">
@@ -11023,16 +11023,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -11052,7 +11052,7 @@
         </is>
       </c>
       <c r="D504" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="505">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -11072,7 +11072,7 @@
         </is>
       </c>
       <c r="D505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -11083,15 +11083,175 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
           <t>£5K-£10K</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr">
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
         <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D506" t="n">
+      <c r="D514" t="n">
         <v>11</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C12" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D12" t="n">
         <v>75</v>
@@ -913,7 +913,7 @@
         <v>205</v>
       </c>
       <c r="K12" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="L12" t="n">
         <v>994</v>
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5461</v>
+        <v>5463</v>
       </c>
       <c r="C13" t="n">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="D13" t="n">
         <v>1172</v>
@@ -953,7 +953,7 @@
         <v>1557</v>
       </c>
       <c r="K13" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L13" t="n">
         <v>12968</v>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="159">
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="165">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="166">

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -489,10 +489,10 @@
         <v>3111</v>
       </c>
       <c r="C2" t="n">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D2" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E2" t="n">
         <v>103</v>
@@ -504,7 +504,7 @@
         <v>35</v>
       </c>
       <c r="H2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I2" t="n">
         <v>320</v>
@@ -513,10 +513,10 @@
         <v>558</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>5548</v>
+        <v>5555</v>
       </c>
     </row>
     <row r="3">
@@ -553,10 +553,10 @@
         <v>78</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="4">
@@ -569,7 +569,7 @@
         <v>351</v>
       </c>
       <c r="C4" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D4" t="n">
         <v>124</v>
@@ -593,7 +593,7 @@
         <v>108</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>939</v>
@@ -633,10 +633,10 @@
         <v>165</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
-        <v>1385</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="6">
@@ -655,7 +655,7 @@
         <v>116</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" t="n">
         <v>29</v>
@@ -673,10 +673,10 @@
         <v>120</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>1007</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="7">
@@ -689,13 +689,13 @@
         <v>507</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D7" t="n">
         <v>199</v>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
         <v>39</v>
@@ -713,10 +713,10 @@
         <v>236</v>
       </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" t="n">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="8">
@@ -753,10 +753,10 @@
         <v>38</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -793,10 +793,10 @@
         <v>32</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -873,10 +873,10 @@
         <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
@@ -889,10 +889,10 @@
         <v>91</v>
       </c>
       <c r="C12" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D12" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" t="n">
         <v>20</v>
@@ -904,7 +904,7 @@
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
         <v>117</v>
@@ -913,10 +913,10 @@
         <v>205</v>
       </c>
       <c r="K12" t="n">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="L12" t="n">
-        <v>994</v>
+        <v>973</v>
       </c>
     </row>
     <row r="13">
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D514"/>
+  <dimension ref="A1:D521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="78">
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="82">
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86">
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96">
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="120">
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
@@ -3548,11 +3548,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3563,16 +3563,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>97</v>
+        <v>30</v>
       </c>
     </row>
     <row r="131">
@@ -3588,11 +3588,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="132">
@@ -3608,11 +3608,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3628,11 +3628,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="134">
@@ -3648,11 +3648,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3668,11 +3668,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136">
@@ -3688,11 +3688,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137">
@@ -3708,11 +3708,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="138">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>109</v>
+        <v>31</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>GUTSHIFT</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>GUTSHIFT</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
     </row>
     <row r="141">
@@ -3788,11 +3788,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
@@ -3803,12 +3803,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -3868,11 +3868,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -3903,16 +3903,16 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -3963,16 +3963,16 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -4028,11 +4028,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4043,16 +4043,16 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -4063,16 +4063,16 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -4118,41 +4118,41 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>GUTSHIFT</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>GUTSHIFT</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4168,11 +4168,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="161">
@@ -4188,11 +4188,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="162">
@@ -4208,11 +4208,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4228,11 +4228,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -4248,11 +4248,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="165">
@@ -4268,11 +4268,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166">
@@ -4283,16 +4283,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
     </row>
     <row r="167">
@@ -4303,16 +4303,16 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="168">
@@ -4328,11 +4328,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="169">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="171">
@@ -4388,11 +4388,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4408,11 +4408,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173">
@@ -4428,11 +4428,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174">
@@ -4448,11 +4448,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="175">
@@ -4468,11 +4468,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>87</v>
+        <v>11</v>
       </c>
     </row>
     <row r="176">
@@ -4483,16 +4483,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="177">
@@ -4503,16 +4503,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>12</v>
+        <v>87</v>
       </c>
     </row>
     <row r="178">
@@ -4528,11 +4528,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="179">
@@ -4548,11 +4548,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -4588,11 +4588,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -4608,11 +4608,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -4628,11 +4628,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="184">
@@ -4648,11 +4648,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="185">
@@ -4663,16 +4663,16 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186">
@@ -4683,16 +4683,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="187">
@@ -4708,11 +4708,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="188">
@@ -4728,11 +4728,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="189">
@@ -4748,11 +4748,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -4768,11 +4768,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -4788,11 +4788,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192">
@@ -4808,11 +4808,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193">
@@ -4823,16 +4823,16 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>148</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -4843,16 +4843,16 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="195">
@@ -4868,11 +4868,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>54</v>
+        <v>149</v>
       </c>
     </row>
     <row r="196">
@@ -4888,11 +4888,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="197">
@@ -4908,11 +4908,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
     </row>
     <row r="198">
@@ -4928,11 +4928,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -4948,11 +4948,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="200">
@@ -4968,11 +4968,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
     </row>
     <row r="201">
@@ -4988,11 +4988,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
     </row>
     <row r="202">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>115</v>
+        <v>54</v>
       </c>
     </row>
     <row r="203">
@@ -5023,16 +5023,16 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="204">
@@ -5043,16 +5043,16 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>115</v>
       </c>
     </row>
     <row r="205">
@@ -5068,11 +5068,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
     </row>
     <row r="206">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -5108,11 +5108,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="208">
@@ -5128,11 +5128,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -5148,11 +5148,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="210">
@@ -5168,11 +5168,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="211">
@@ -5188,11 +5188,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="212">
@@ -5208,11 +5208,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
     </row>
     <row r="213">
@@ -5223,16 +5223,16 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214">
@@ -5243,16 +5243,16 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
     </row>
     <row r="215">
@@ -5268,11 +5268,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="216">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -5308,11 +5308,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218">
@@ -5323,16 +5323,16 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
@@ -5343,16 +5343,16 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="220">
@@ -5368,11 +5368,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="221">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -5408,11 +5408,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="223">
@@ -5428,11 +5428,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
@@ -5448,11 +5448,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
@@ -5468,11 +5468,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="226">
@@ -5488,11 +5488,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="227">
@@ -5503,16 +5503,16 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -5523,16 +5523,16 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="229">
@@ -5548,11 +5548,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="230">
@@ -5568,11 +5568,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -5588,11 +5588,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="232">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -5628,11 +5628,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="234">
@@ -5648,11 +5648,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -5668,11 +5668,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="236">
@@ -5688,11 +5688,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="237">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -5723,16 +5723,16 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
     </row>
     <row r="239">
@@ -5748,11 +5748,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="240">
@@ -5768,11 +5768,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
@@ -5783,16 +5783,16 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -5803,16 +5803,16 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -5823,16 +5823,16 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="244">
@@ -5848,11 +5848,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="245">
@@ -5868,11 +5868,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="246">
@@ -5888,11 +5888,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -5908,11 +5908,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248">
@@ -5928,11 +5928,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="249">
@@ -5948,71 +5948,71 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="253">
@@ -6023,16 +6023,16 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -6063,12 +6063,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -6083,16 +6083,16 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -6148,11 +6148,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260">
@@ -6168,11 +6168,11 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
@@ -6183,16 +6183,16 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262">
@@ -6203,16 +6203,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -6223,16 +6223,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264">
@@ -6248,11 +6248,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="265">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -6288,11 +6288,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="267">
@@ -6308,11 +6308,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
@@ -6328,11 +6328,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -6348,11 +6348,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="270">
@@ -6363,16 +6363,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="271">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -6403,16 +6403,16 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="273">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="274">
@@ -6448,11 +6448,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -6463,16 +6463,16 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6552,7 +6552,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -6603,16 +6603,16 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -6643,16 +6643,16 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="289">
@@ -6743,16 +6743,16 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
@@ -6763,16 +6763,16 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -6783,16 +6783,16 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -6803,16 +6803,16 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="293">
@@ -6828,127 +6828,127 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>279</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D299" t="n">
@@ -6968,11 +6968,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>152</v>
+        <v>279</v>
       </c>
     </row>
     <row r="301">
@@ -6988,11 +6988,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="302">
@@ -7008,11 +7008,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="303">
@@ -7023,16 +7023,16 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
@@ -7043,16 +7043,16 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="305">
@@ -7063,16 +7063,16 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="306">
@@ -7083,16 +7083,16 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>3</v>
+        <v>152</v>
       </c>
     </row>
     <row r="307">
@@ -7103,16 +7103,16 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="308">
@@ -7123,16 +7123,16 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="309">
@@ -7148,11 +7148,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="310">
@@ -7168,11 +7168,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -7183,16 +7183,16 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -7203,16 +7203,16 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -7223,16 +7223,16 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -7243,16 +7243,16 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="315">
@@ -7263,16 +7263,16 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -7283,16 +7283,16 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="317">
@@ -7303,16 +7303,16 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="318">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D318" t="n">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D319" t="n">
@@ -7358,17 +7358,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D320" t="n">
@@ -7378,57 +7378,57 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D323" t="n">
@@ -7438,41 +7438,41 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="326">
@@ -7483,16 +7483,16 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -7503,16 +7503,16 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D328" t="n">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D329" t="n">
@@ -7563,16 +7563,16 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="331">
@@ -7588,11 +7588,11 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="332">
@@ -7608,11 +7608,11 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -7628,11 +7628,11 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -7643,16 +7643,16 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -7663,16 +7663,16 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -7683,16 +7683,16 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D337" t="n">
@@ -7723,16 +7723,16 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="339">
@@ -7743,16 +7743,16 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="340">
@@ -7768,11 +7768,11 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="341">
@@ -7788,11 +7788,11 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="342">
@@ -7803,16 +7803,16 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -7823,16 +7823,16 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="346">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -7892,7 +7892,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="347">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="348">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -7932,7 +7932,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
     </row>
     <row r="349">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D349" t="n">
@@ -7963,16 +7963,16 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="351">
@@ -7983,16 +7983,16 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="352">
@@ -8003,16 +8003,16 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
@@ -8023,16 +8023,16 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -8048,11 +8048,11 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="355">
@@ -8068,11 +8068,11 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -8088,11 +8088,11 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="357">
@@ -8103,16 +8103,16 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="358">
@@ -8123,16 +8123,16 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="359">
@@ -8143,16 +8143,16 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="360">
@@ -8163,16 +8163,16 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="361">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D361" t="n">
@@ -8203,16 +8203,16 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="363">
@@ -8228,11 +8228,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="364">
@@ -8248,11 +8248,11 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="365">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D366" t="n">
@@ -8303,16 +8303,16 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="368">
@@ -8323,16 +8323,16 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="369">
@@ -8343,16 +8343,16 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="370">
@@ -8363,16 +8363,16 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -8383,16 +8383,16 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="372">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D372" t="n">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D373" t="n">
@@ -8443,16 +8443,16 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="375">
@@ -8468,11 +8468,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="376">
@@ -8483,16 +8483,16 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
@@ -8503,16 +8503,16 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="378">
@@ -8523,16 +8523,16 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="379">
@@ -8543,16 +8543,16 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -8563,16 +8563,16 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
@@ -8583,16 +8583,16 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="382">
@@ -8608,11 +8608,11 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="383">
@@ -8628,11 +8628,11 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
@@ -8648,11 +8648,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="385">
@@ -8668,11 +8668,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -8683,16 +8683,16 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -8703,16 +8703,16 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D388" t="n">
@@ -8743,16 +8743,16 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="390">
@@ -8763,16 +8763,16 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="391">
@@ -8783,16 +8783,16 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="392">
@@ -8803,32 +8803,32 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D393" t="n">
@@ -8838,57 +8838,57 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D396" t="n">
@@ -8898,17 +8898,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D397" t="n">
@@ -8918,41 +8918,41 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="400">
@@ -8963,16 +8963,16 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401">
@@ -8983,16 +8983,16 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D402" t="n">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D403" t="n">
@@ -9043,16 +9043,16 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="405">
@@ -9063,16 +9063,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="406">
@@ -9083,16 +9083,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="407">
@@ -9103,16 +9103,16 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="408">
@@ -9123,16 +9123,16 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -9143,16 +9143,16 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -9163,16 +9163,16 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -9183,16 +9183,16 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="412">
@@ -9203,16 +9203,16 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413">
@@ -9223,16 +9223,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -9243,16 +9243,16 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="415">
@@ -9268,11 +9268,11 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="416">
@@ -9288,11 +9288,11 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="417">
@@ -9308,11 +9308,11 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418">
@@ -9323,16 +9323,16 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -9343,16 +9343,16 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="420">
@@ -9363,16 +9363,16 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="421">
@@ -9383,16 +9383,16 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="422">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D422" t="n">
@@ -9423,16 +9423,16 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="424">
@@ -9443,16 +9443,16 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -9463,16 +9463,16 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="426">
@@ -9483,16 +9483,16 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427">
@@ -9503,16 +9503,16 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="428">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D428" t="n">
@@ -9543,16 +9543,16 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
@@ -9563,16 +9563,16 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="431">
@@ -9588,11 +9588,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="432">
@@ -9608,11 +9608,11 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
@@ -9623,12 +9623,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D433" t="n">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D434" t="n">
@@ -9663,16 +9663,16 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -9683,16 +9683,16 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437">
@@ -9703,16 +9703,16 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438">
@@ -9723,16 +9723,16 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="439">
@@ -9743,12 +9743,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D439" t="n">
@@ -9763,16 +9763,16 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441">
@@ -9783,16 +9783,16 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442">
@@ -9803,16 +9803,16 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="443">
@@ -9828,67 +9828,67 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D446" t="n">
@@ -9898,81 +9898,81 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
@@ -9988,11 +9988,11 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>116</v>
+        <v>20</v>
       </c>
     </row>
     <row r="452">
@@ -10003,16 +10003,16 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="453">
@@ -10023,12 +10023,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D453" t="n">
@@ -10043,16 +10043,16 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="455">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="456">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="457">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="458">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10132,7 +10132,7 @@
         </is>
       </c>
       <c r="D458" t="n">
-        <v>17</v>
+        <v>116</v>
       </c>
     </row>
     <row r="459">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="460">
@@ -10163,16 +10163,16 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461">
@@ -10183,16 +10183,16 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="462">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -10232,7 +10232,7 @@
         </is>
       </c>
       <c r="D463" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="464">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="D464" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="465">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="466">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="D466" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="467">
@@ -10303,16 +10303,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="468">
@@ -10323,16 +10323,16 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="469">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D469" t="n">
@@ -10363,16 +10363,16 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="471">
@@ -10383,16 +10383,16 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="472">
@@ -10403,16 +10403,16 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="473">
@@ -10428,11 +10428,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="474">
@@ -10448,11 +10448,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -10463,16 +10463,16 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="476">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D476" t="n">
@@ -10503,16 +10503,16 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="478">
@@ -10523,16 +10523,16 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="479">
@@ -10543,16 +10543,16 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="480">
@@ -10563,16 +10563,16 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="481">
@@ -10583,16 +10583,16 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="482">
@@ -10608,11 +10608,11 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="483">
@@ -10623,16 +10623,16 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="484">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -10652,7 +10652,7 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="485">
@@ -10663,16 +10663,16 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="486">
@@ -10683,12 +10683,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D486" t="n">
@@ -10703,16 +10703,16 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="488">
@@ -10723,12 +10723,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D488" t="n">
@@ -10743,16 +10743,16 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="490">
@@ -10763,16 +10763,16 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D491" t="n">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -10812,7 +10812,7 @@
         </is>
       </c>
       <c r="D492" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -10832,7 +10832,7 @@
         </is>
       </c>
       <c r="D493" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="495">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -10872,7 +10872,7 @@
         </is>
       </c>
       <c r="D495" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="496">
@@ -10883,16 +10883,16 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="497">
@@ -10903,16 +10903,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="498">
@@ -10923,16 +10923,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="499">
@@ -10943,16 +10943,16 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="500">
@@ -10963,16 +10963,16 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -10983,16 +10983,16 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="502">
@@ -11008,11 +11008,11 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="503">
@@ -11023,16 +11023,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -11043,16 +11043,16 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="505">
@@ -11063,16 +11063,16 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="506">
@@ -11083,16 +11083,16 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="507">
@@ -11103,16 +11103,16 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="508">
@@ -11123,16 +11123,16 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="509">
@@ -11143,16 +11143,16 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="510">
@@ -11163,12 +11163,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D510" t="n">
@@ -11183,16 +11183,16 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="512">
@@ -11203,16 +11203,16 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="513">
@@ -11223,16 +11223,16 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="514">
@@ -11248,10 +11248,150 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
+          <t>Black/African</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D514" t="n">
+      <c r="D521" t="n">
         <v>11</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -913,10 +913,10 @@
         <v>205</v>
       </c>
       <c r="K12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L12" t="n">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="13">
@@ -953,10 +953,10 @@
         <v>1557</v>
       </c>
       <c r="K13" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L13" t="n">
-        <v>12968</v>
+        <v>12969</v>
       </c>
     </row>
   </sheetData>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="167">

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -486,19 +486,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3111</v>
+        <v>3107</v>
       </c>
       <c r="C2" t="n">
         <v>763</v>
       </c>
       <c r="D2" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E2" t="n">
         <v>103</v>
       </c>
       <c r="F2" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G2" t="n">
         <v>35</v>
@@ -507,16 +507,16 @@
         <v>55</v>
       </c>
       <c r="I2" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J2" t="n">
         <v>558</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>5555</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="3">
@@ -526,13 +526,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C3" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E3" t="n">
         <v>16</v>
@@ -553,10 +553,10 @@
         <v>78</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="4">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C4" t="n">
         <v>207</v>
@@ -575,7 +575,7 @@
         <v>124</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
         <v>26</v>
@@ -593,10 +593,10 @@
         <v>108</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="5">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C5" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D5" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
         <v>33</v>
@@ -627,16 +627,16 @@
         <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J5" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L5" t="n">
-        <v>1388</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="6">
@@ -646,13 +646,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C6" t="n">
         <v>238</v>
       </c>
       <c r="D6" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E6" t="n">
         <v>31</v>
@@ -670,13 +670,13 @@
         <v>103</v>
       </c>
       <c r="J6" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="7">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
         <v>199</v>
@@ -707,16 +707,16 @@
         <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J7" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K7" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L7" t="n">
-        <v>1665</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="8">
@@ -729,10 +729,10 @@
         <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
         <v>13</v>
@@ -753,10 +753,10 @@
         <v>38</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" t="n">
         <v>59</v>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
@@ -812,7 +812,7 @@
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" t="n">
         <v>366</v>
@@ -895,7 +895,7 @@
         <v>74</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
         <v>9</v>
@@ -913,10 +913,10 @@
         <v>205</v>
       </c>
       <c r="K12" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="L12" t="n">
-        <v>974</v>
+        <v>986</v>
       </c>
     </row>
     <row r="13">
@@ -926,19 +926,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5463</v>
+        <v>5452</v>
       </c>
       <c r="C13" t="n">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="D13" t="n">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="E13" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F13" t="n">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G13" t="n">
         <v>67</v>
@@ -947,16 +947,16 @@
         <v>124</v>
       </c>
       <c r="I13" t="n">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="J13" t="n">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="K13" t="n">
-        <v>166</v>
+        <v>226</v>
       </c>
       <c r="L13" t="n">
-        <v>12969</v>
+        <v>13002</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D521"/>
+  <dimension ref="A1:D528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46">
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="53">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="55">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3019</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="57">
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="67">
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75">
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="78">
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="80">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85">
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="88">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="92">
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96">
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="97">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104">
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="106">
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114">
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="115">
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="122">
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="123">
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="125">
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="132">
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="162">
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="167">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="176">
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="184">
@@ -4652,7 +4652,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="185">
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="186">
@@ -4872,7 +4872,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="196">
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="202">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="203">
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="204">
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="205">
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="212">
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="213">
@@ -5232,7 +5232,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214">
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="215">
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219">
@@ -5348,11 +5348,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
@@ -5363,16 +5363,16 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="221">
@@ -5388,11 +5388,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="222">
@@ -5408,11 +5408,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -5428,11 +5428,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="224">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -5468,11 +5468,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
@@ -5488,11 +5488,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="227">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228">
@@ -5528,11 +5528,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -5543,16 +5543,16 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
     </row>
     <row r="230">
@@ -5568,11 +5568,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="231">
@@ -5588,11 +5588,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
@@ -5608,11 +5608,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233">
@@ -5628,11 +5628,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -5648,11 +5648,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="235">
@@ -5668,11 +5668,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -5688,11 +5688,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="237">
@@ -5708,11 +5708,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="238">
@@ -5728,11 +5728,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>77</v>
+        <v>7</v>
       </c>
     </row>
     <row r="239">
@@ -5743,16 +5743,16 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>6</v>
+        <v>77</v>
       </c>
     </row>
     <row r="240">
@@ -5768,11 +5768,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="241">
@@ -5788,11 +5788,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -5808,11 +5808,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -5828,11 +5828,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
@@ -5843,16 +5843,16 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="245">
@@ -5868,11 +5868,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="246">
@@ -5888,11 +5888,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="247">
@@ -5908,11 +5908,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
@@ -5928,11 +5928,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="249">
@@ -5948,11 +5948,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="250">
@@ -5968,11 +5968,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="251">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="252">
@@ -6008,31 +6008,31 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="254">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -6088,11 +6088,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="259">
@@ -6143,16 +6143,16 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -6168,11 +6168,11 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="261">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -6228,11 +6228,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
@@ -6243,16 +6243,16 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="265">
@@ -6268,11 +6268,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="266">
@@ -6288,11 +6288,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267">
@@ -6308,11 +6308,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="268">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -6348,11 +6348,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -6368,11 +6368,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="271">
@@ -6388,11 +6388,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="272">
@@ -6408,11 +6408,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="273">
@@ -6423,16 +6423,16 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="274">
@@ -6448,11 +6448,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -6508,11 +6508,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
@@ -6528,11 +6528,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -6568,11 +6568,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -6608,11 +6608,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
@@ -6623,16 +6623,16 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="284">
@@ -6648,11 +6648,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="285">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -6688,11 +6688,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
@@ -6708,11 +6708,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288">
@@ -6723,16 +6723,16 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="289">
@@ -6748,11 +6748,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290">
@@ -6768,11 +6768,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
@@ -6788,11 +6788,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292">
@@ -6808,11 +6808,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
@@ -6823,16 +6823,16 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="294">
@@ -6848,11 +6848,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="295">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D295" t="n">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="297">
@@ -6908,11 +6908,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="298">
@@ -6928,11 +6928,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
@@ -6948,31 +6948,31 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>279</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301">
@@ -6988,11 +6988,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>5</v>
+        <v>279</v>
       </c>
     </row>
     <row r="302">
@@ -7008,11 +7008,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303">
@@ -7028,11 +7028,11 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
     </row>
     <row r="304">
@@ -7048,11 +7048,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -7068,11 +7068,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="306">
@@ -7088,11 +7088,11 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>152</v>
+        <v>5</v>
       </c>
     </row>
     <row r="307">
@@ -7108,11 +7108,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>46</v>
+        <v>152</v>
       </c>
     </row>
     <row r="308">
@@ -7128,11 +7128,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="309">
@@ -7143,16 +7143,16 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
@@ -7163,16 +7163,16 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="311">
@@ -7188,11 +7188,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="312">
@@ -7208,11 +7208,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D313" t="n">
@@ -7248,11 +7248,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -7268,11 +7268,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -7288,11 +7288,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="317">
@@ -7303,16 +7303,16 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -7323,16 +7323,16 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="319">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="320">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D320" t="n">
@@ -7383,16 +7383,16 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7412,7 +7412,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D323" t="n">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325">
@@ -7463,72 +7463,72 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D328" t="n">
@@ -7538,12 +7538,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -7568,11 +7568,11 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -7583,16 +7583,16 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -7623,16 +7623,16 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="334">
@@ -7643,16 +7643,16 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="335">
@@ -7668,11 +7668,11 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="336">
@@ -7688,11 +7688,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D337" t="n">
@@ -7728,11 +7728,11 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
@@ -7748,11 +7748,11 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="340">
@@ -7763,16 +7763,16 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
@@ -7783,16 +7783,16 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
@@ -7803,16 +7803,16 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="343">
@@ -7823,16 +7823,16 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="344">
@@ -7848,11 +7848,11 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="345">
@@ -7868,11 +7868,11 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="346">
@@ -7888,11 +7888,11 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
@@ -7908,11 +7908,11 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="348">
@@ -7923,16 +7923,16 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="349">
@@ -7943,16 +7943,16 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="350">
@@ -7963,16 +7963,16 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="351">
@@ -7983,16 +7983,16 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="352">
@@ -8008,11 +8008,11 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D353" t="n">
@@ -8043,16 +8043,16 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -8063,16 +8063,16 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -8083,16 +8083,16 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -8103,16 +8103,16 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -8128,11 +8128,11 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
     </row>
     <row r="359">
@@ -8148,11 +8148,11 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
@@ -8168,11 +8168,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="361">
@@ -8188,11 +8188,11 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="362">
@@ -8208,11 +8208,11 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
     </row>
     <row r="363">
@@ -8223,16 +8223,16 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="364">
@@ -8243,16 +8243,16 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="365">
@@ -8263,16 +8263,16 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="366">
@@ -8283,16 +8283,16 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="367">
@@ -8308,11 +8308,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="368">
@@ -8328,11 +8328,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="369">
@@ -8348,11 +8348,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
@@ -8368,11 +8368,11 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -8388,11 +8388,11 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="372">
@@ -8403,16 +8403,16 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="373">
@@ -8423,16 +8423,16 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="374">
@@ -8443,16 +8443,16 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="375">
@@ -8463,16 +8463,16 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="376">
@@ -8483,16 +8483,16 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="377">
@@ -8503,16 +8503,16 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -8523,16 +8523,16 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
@@ -8548,11 +8548,11 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -8588,11 +8588,11 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
@@ -8603,16 +8603,16 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D383" t="n">
@@ -8643,16 +8643,16 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385">
@@ -8663,16 +8663,16 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="386">
@@ -8688,11 +8688,11 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="387">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D387" t="n">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="389">
@@ -8748,11 +8748,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -8768,11 +8768,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="391">
@@ -8788,11 +8788,11 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392">
@@ -8803,16 +8803,16 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="393">
@@ -8823,16 +8823,16 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="394">
@@ -8843,16 +8843,16 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="395">
@@ -8863,16 +8863,16 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="396">
@@ -8883,16 +8883,16 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D397" t="n">
@@ -8923,16 +8923,16 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="399">
@@ -8948,27 +8948,27 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D400" t="n">
@@ -8978,17 +8978,17 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -8998,41 +8998,41 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="404">
@@ -9043,12 +9043,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D404" t="n">
@@ -9063,16 +9063,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="406">
@@ -9083,16 +9083,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -9112,7 +9112,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="408">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D408" t="n">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="411">
@@ -9183,16 +9183,16 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -9203,12 +9203,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D412" t="n">
@@ -9223,16 +9223,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -9248,11 +9248,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="415">
@@ -9263,16 +9263,16 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
@@ -9283,16 +9283,16 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
@@ -9303,16 +9303,16 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="418">
@@ -9328,11 +9328,11 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="419">
@@ -9348,11 +9348,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="420">
@@ -9368,11 +9368,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -9388,11 +9388,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422">
@@ -9408,11 +9408,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="423">
@@ -9428,11 +9428,11 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="424">
@@ -9443,16 +9443,16 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="425">
@@ -9463,16 +9463,16 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="426">
@@ -9483,16 +9483,16 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="427">
@@ -9508,11 +9508,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -9523,16 +9523,16 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D429" t="n">
@@ -9563,16 +9563,16 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -9583,16 +9583,16 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="432">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D432" t="n">
@@ -9623,12 +9623,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D433" t="n">
@@ -9643,16 +9643,16 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="435">
@@ -9668,11 +9668,11 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="436">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D436" t="n">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D437" t="n">
@@ -9728,11 +9728,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439">
@@ -9743,16 +9743,16 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="440">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="443">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="444">
@@ -9843,16 +9843,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -9883,16 +9883,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -9908,11 +9908,11 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="448">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D448" t="n">
@@ -9948,11 +9948,11 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
@@ -9968,111 +9968,111 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="456">
@@ -10088,11 +10088,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="457">
@@ -10108,11 +10108,11 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="458">
@@ -10128,11 +10128,11 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>116</v>
+        <v>1</v>
       </c>
     </row>
     <row r="459">
@@ -10143,16 +10143,16 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="460">
@@ -10163,16 +10163,16 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="461">
@@ -10183,16 +10183,16 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="462">
@@ -10203,16 +10203,16 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="463">
@@ -10223,16 +10223,16 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>7</v>
+        <v>116</v>
       </c>
     </row>
     <row r="464">
@@ -10248,11 +10248,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="465">
@@ -10268,11 +10268,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="466">
@@ -10283,16 +10283,16 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="467">
@@ -10303,16 +10303,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468">
@@ -10323,16 +10323,16 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="469">
@@ -10343,16 +10343,16 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="470">
@@ -10363,16 +10363,16 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="471">
@@ -10388,11 +10388,11 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="472">
@@ -10408,11 +10408,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="473">
@@ -10423,16 +10423,16 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
@@ -10443,16 +10443,16 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475">
@@ -10463,16 +10463,16 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="476">
@@ -10483,16 +10483,16 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="477">
@@ -10503,16 +10503,16 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="478">
@@ -10528,11 +10528,11 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="479">
@@ -10548,11 +10548,11 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="481">
@@ -10588,11 +10588,11 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
@@ -10603,16 +10603,16 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="483">
@@ -10623,16 +10623,16 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="484">
@@ -10643,16 +10643,16 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="485">
@@ -10663,16 +10663,16 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="486">
@@ -10683,16 +10683,16 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="487">
@@ -10703,16 +10703,16 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
     </row>
     <row r="488">
@@ -10728,11 +10728,11 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="489">
@@ -10748,11 +10748,11 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490">
@@ -10763,16 +10763,16 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="491">
@@ -10783,16 +10783,16 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="492">
@@ -10803,16 +10803,16 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="493">
@@ -10823,16 +10823,16 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="494">
@@ -10843,12 +10843,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D494" t="n">
@@ -10863,16 +10863,16 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="496">
@@ -10883,16 +10883,16 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -10903,12 +10903,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D497" t="n">
@@ -10923,16 +10923,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -10943,16 +10943,16 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500">
@@ -10963,16 +10963,16 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="501">
@@ -10988,11 +10988,11 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="502">
@@ -11003,16 +11003,16 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="503">
@@ -11023,16 +11023,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -11043,16 +11043,16 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505">
@@ -11063,16 +11063,16 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="506">
@@ -11083,12 +11083,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D506" t="n">
@@ -11103,16 +11103,16 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="508">
@@ -11128,11 +11128,11 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="509">
@@ -11148,11 +11148,11 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -11163,16 +11163,16 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="511">
@@ -11183,16 +11183,16 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="512">
@@ -11203,16 +11203,16 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="513">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D513" t="n">
@@ -11243,16 +11243,16 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="515">
@@ -11263,16 +11263,16 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="516">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D516" t="n">
@@ -11303,16 +11303,16 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="518">
@@ -11323,16 +11323,16 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519">
@@ -11343,16 +11343,16 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="520">
@@ -11368,11 +11368,11 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="521">
@@ -11388,10 +11388,150 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
+          <t>Faceless</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D521" t="n">
+      <c r="D528" t="n">
         <v>11</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -529,10 +529,10 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>3067</v>
+        <v>3071</v>
       </c>
       <c r="C2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D2">
         <v>353</v>
@@ -550,16 +550,16 @@
         <v>54</v>
       </c>
       <c r="I2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="J2">
         <v>490</v>
       </c>
       <c r="K2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L2">
-        <v>5634</v>
+        <v>5646</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -567,7 +567,7 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C3">
         <v>130</v>
@@ -597,7 +597,7 @@
         <v>27</v>
       </c>
       <c r="L3">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -605,13 +605,13 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C4">
         <v>204</v>
       </c>
       <c r="D4">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E4">
         <v>23</v>
@@ -635,7 +635,7 @@
         <v>33</v>
       </c>
       <c r="L4">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -681,7 +681,7 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C6">
         <v>236</v>
@@ -708,10 +708,10 @@
         <v>111</v>
       </c>
       <c r="K6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L6">
-        <v>1025</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -722,7 +722,7 @@
         <v>499</v>
       </c>
       <c r="C7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D7">
         <v>194</v>
@@ -749,7 +749,7 @@
         <v>89</v>
       </c>
       <c r="L7">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -909,13 +909,13 @@
         <v>22</v>
       </c>
       <c r="B12">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C12">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D12">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12">
         <v>20</v>
@@ -930,16 +930,16 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J12">
         <v>199</v>
       </c>
       <c r="K12">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L12">
-        <v>951</v>
+        <v>933</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1519,7 +1519,7 @@
         <v>2</v>
       </c>
       <c r="D38">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1547,7 +1547,7 @@
         <v>8</v>
       </c>
       <c r="D40">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1603,7 +1603,7 @@
         <v>3</v>
       </c>
       <c r="D44">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1617,7 +1617,7 @@
         <v>10</v>
       </c>
       <c r="D45">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1631,7 +1631,7 @@
         <v>1</v>
       </c>
       <c r="D46">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1645,7 +1645,7 @@
         <v>2</v>
       </c>
       <c r="D47">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1673,7 +1673,7 @@
         <v>8</v>
       </c>
       <c r="D49">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1757,7 +1757,7 @@
         <v>10</v>
       </c>
       <c r="D55">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1771,7 +1771,7 @@
         <v>1</v>
       </c>
       <c r="D56">
-        <v>2971</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1883,7 +1883,7 @@
         <v>3</v>
       </c>
       <c r="D64">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1911,7 +1911,7 @@
         <v>1</v>
       </c>
       <c r="D66">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2065,7 +2065,7 @@
         <v>2</v>
       </c>
       <c r="D77">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2597,7 +2597,7 @@
         <v>1</v>
       </c>
       <c r="D115">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2737,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="D125">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3241,7 +3241,7 @@
         <v>2</v>
       </c>
       <c r="D161">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3255,7 +3255,7 @@
         <v>8</v>
       </c>
       <c r="D162">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3311,7 +3311,7 @@
         <v>10</v>
       </c>
       <c r="D166">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3339,7 +3339,7 @@
         <v>2</v>
       </c>
       <c r="D168">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3367,7 +3367,7 @@
         <v>8</v>
       </c>
       <c r="D170">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3451,7 +3451,7 @@
         <v>10</v>
       </c>
       <c r="D176">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4319,7 +4319,7 @@
         <v>10</v>
       </c>
       <c r="D238">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5201,7 +5201,7 @@
         <v>2</v>
       </c>
       <c r="D301">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5229,7 +5229,7 @@
         <v>8</v>
       </c>
       <c r="D303">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5327,7 +5327,7 @@
         <v>1</v>
       </c>
       <c r="D310">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5341,7 +5341,7 @@
         <v>2</v>
       </c>
       <c r="D311">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5369,7 +5369,7 @@
         <v>8</v>
       </c>
       <c r="D313">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5453,7 +5453,7 @@
         <v>1</v>
       </c>
       <c r="D319">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="320" spans="1:4">

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -793,10 +793,10 @@
         <v>30</v>
       </c>
       <c r="K9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L9" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -889,7 +889,7 @@
         <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D12" t="n">
         <v>71</v>
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="L12" t="n">
-        <v>933</v>
+        <v>948</v>
       </c>
     </row>
     <row r="13">
@@ -929,7 +929,7 @@
         <v>5354</v>
       </c>
       <c r="C13" t="n">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="D13" t="n">
         <v>1146</v>
@@ -953,10 +953,10 @@
         <v>1421</v>
       </c>
       <c r="K13" t="n">
-        <v>643</v>
+        <v>658</v>
       </c>
       <c r="L13" t="n">
-        <v>13110</v>
+        <v>13126</v>
       </c>
     </row>
   </sheetData>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="167">
@@ -4512,7 +4512,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="178">
@@ -4872,7 +4872,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="196">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="198">
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="204">
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="205">
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="240">
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="418">
@@ -9412,7 +9412,7 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="423">
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="425">
@@ -9952,7 +9952,7 @@
         </is>
       </c>
       <c r="D449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -489,7 +489,7 @@
         <v>3071</v>
       </c>
       <c r="C2" t="n">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D2" t="n">
         <v>353</v>
@@ -513,10 +513,10 @@
         <v>490</v>
       </c>
       <c r="K2" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L2" t="n">
-        <v>5646</v>
+        <v>5648</v>
       </c>
     </row>
     <row r="3">
@@ -673,10 +673,10 @@
         <v>111</v>
       </c>
       <c r="K6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L6" t="n">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="7">
@@ -713,10 +713,10 @@
         <v>223</v>
       </c>
       <c r="K7" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="L7" t="n">
-        <v>1702</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="8">
@@ -793,10 +793,10 @@
         <v>30</v>
       </c>
       <c r="K9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -889,7 +889,7 @@
         <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D12" t="n">
         <v>71</v>
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="L12" t="n">
-        <v>948</v>
+        <v>935</v>
       </c>
     </row>
     <row r="13">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="48">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76">
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="125">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="167">
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194">
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="204">

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -513,10 +513,10 @@
         <v>490</v>
       </c>
       <c r="K2" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L2" t="n">
-        <v>5648</v>
+        <v>5647</v>
       </c>
     </row>
     <row r="3">
@@ -673,10 +673,10 @@
         <v>111</v>
       </c>
       <c r="K6" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L6" t="n">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L12" t="n">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="13">
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D529"/>
+  <dimension ref="A1:D530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="125">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="167">
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229">
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="239">
@@ -7643,16 +7643,16 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -7668,11 +7668,11 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="336">
@@ -7688,11 +7688,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -7708,11 +7708,11 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="338">
@@ -7728,11 +7728,11 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D339" t="n">
@@ -7768,11 +7768,11 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341">
@@ -7788,11 +7788,11 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
@@ -7808,11 +7808,11 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="343">
@@ -7823,16 +7823,16 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="344">
@@ -7848,11 +7848,11 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="345">
@@ -7868,11 +7868,11 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="346">
@@ -7888,11 +7888,11 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
@@ -7908,11 +7908,11 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="348">
@@ -7928,11 +7928,11 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="349">
@@ -7948,11 +7948,11 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="350">
@@ -7968,11 +7968,11 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="351">
@@ -7983,16 +7983,16 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="352">
@@ -8008,11 +8008,11 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353">
@@ -8028,11 +8028,11 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -8048,11 +8048,11 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -8068,11 +8068,11 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -8088,11 +8088,11 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -8103,16 +8103,16 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -8128,11 +8128,11 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="359">
@@ -8148,11 +8148,11 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
@@ -8168,11 +8168,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="361">
@@ -8188,11 +8188,11 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="362">
@@ -8208,11 +8208,11 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="363">
@@ -8228,11 +8228,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="364">
@@ -8248,11 +8248,11 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="365">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
     </row>
     <row r="366">
@@ -8283,16 +8283,16 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="367">
@@ -8308,11 +8308,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="368">
@@ -8328,11 +8328,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="369">
@@ -8348,11 +8348,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
@@ -8368,11 +8368,11 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -8388,11 +8388,11 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="372">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D372" t="n">
@@ -8428,11 +8428,11 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="374">
@@ -8448,11 +8448,11 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="375">
@@ -8463,16 +8463,16 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="376">
@@ -8488,11 +8488,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="377">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D377" t="n">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D378" t="n">
@@ -8543,16 +8543,16 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -8568,11 +8568,11 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381">
@@ -8588,11 +8588,11 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D382" t="n">
@@ -8628,11 +8628,11 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -8648,11 +8648,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385">
@@ -8668,11 +8668,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386">
@@ -8683,16 +8683,16 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="387">
@@ -8708,11 +8708,11 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="388">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="389">
@@ -8748,11 +8748,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="390">
@@ -8768,11 +8768,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -8788,11 +8788,11 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="392">
@@ -8808,11 +8808,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
@@ -8828,11 +8828,11 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="394">
@@ -8848,11 +8848,11 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="395">
@@ -8868,11 +8868,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="396">
@@ -8883,16 +8883,16 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="397">
@@ -8908,11 +8908,11 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -8928,11 +8928,11 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="399">
@@ -8943,16 +8943,16 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="400">
@@ -8968,11 +8968,11 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="401">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -9008,11 +9008,11 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="403">
@@ -9028,31 +9028,31 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="405">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D405" t="n">
@@ -9088,11 +9088,11 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407">
@@ -9108,11 +9108,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="408">
@@ -9128,11 +9128,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="409">
@@ -9143,16 +9143,16 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="410">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D411" t="n">
@@ -9208,11 +9208,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413">
@@ -9223,16 +9223,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -9248,11 +9248,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="415">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D415" t="n">
@@ -9288,11 +9288,11 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
@@ -9303,16 +9303,16 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="418">
@@ -9328,11 +9328,11 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="419">
@@ -9348,11 +9348,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="420">
@@ -9368,11 +9368,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -9388,11 +9388,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="422">
@@ -9408,11 +9408,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="423">
@@ -9428,11 +9428,11 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="424">
@@ -9448,11 +9448,11 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="425">
@@ -9468,11 +9468,11 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="426">
@@ -9483,16 +9483,16 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="427">
@@ -9508,11 +9508,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D428" t="n">
@@ -9548,11 +9548,11 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="430">
@@ -9563,16 +9563,16 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="431">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D431" t="n">
@@ -9608,11 +9608,11 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
@@ -9623,16 +9623,16 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="434">
@@ -9648,11 +9648,11 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="435">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D435" t="n">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D436" t="n">
@@ -9708,11 +9708,11 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438">
@@ -9728,11 +9728,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="439">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D439" t="n">
@@ -9768,11 +9768,11 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441">
@@ -9783,16 +9783,16 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="442">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D442" t="n">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D443" t="n">
@@ -9848,11 +9848,11 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445">
@@ -9863,16 +9863,16 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="446">
@@ -9888,11 +9888,11 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="447">
@@ -9908,11 +9908,11 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="448">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D448" t="n">
@@ -9948,11 +9948,11 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
@@ -9968,11 +9968,11 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
@@ -9988,11 +9988,11 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="452">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D452" t="n">
@@ -10028,31 +10028,31 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
@@ -10068,11 +10068,11 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="456">
@@ -10088,11 +10088,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="457">
@@ -10108,11 +10108,11 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -10128,11 +10128,11 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="459">
@@ -10148,11 +10148,11 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="460">
@@ -10168,11 +10168,11 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="461">
@@ -10188,11 +10188,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="462">
@@ -10208,11 +10208,11 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>115</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -10223,16 +10223,16 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>4</v>
+        <v>115</v>
       </c>
     </row>
     <row r="464">
@@ -10248,11 +10248,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="465">
@@ -10268,11 +10268,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="466">
@@ -10288,11 +10288,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="467">
@@ -10308,11 +10308,11 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D468" t="n">
@@ -10348,11 +10348,11 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="470">
@@ -10368,11 +10368,11 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="471">
@@ -10383,16 +10383,16 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="472">
@@ -10408,11 +10408,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="473">
@@ -10428,11 +10428,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="474">
@@ -10448,11 +10448,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D476" t="n">
@@ -10508,11 +10508,11 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="478">
@@ -10523,16 +10523,16 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="479">
@@ -10548,11 +10548,11 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="480">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -10588,11 +10588,11 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="482">
@@ -10608,11 +10608,11 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D483" t="n">
@@ -10648,11 +10648,11 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="485">
@@ -10668,11 +10668,11 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="486">
@@ -10688,11 +10688,11 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="487">
@@ -10708,11 +10708,11 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488">
@@ -10723,16 +10723,16 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="489">
@@ -10748,11 +10748,11 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="490">
@@ -10768,11 +10768,11 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="491">
@@ -10788,11 +10788,11 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="492">
@@ -10808,11 +10808,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="493">
@@ -10828,11 +10828,11 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -10848,11 +10848,11 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="495">
@@ -10868,11 +10868,11 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="496">
@@ -10888,11 +10888,11 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="497">
@@ -10903,16 +10903,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="498">
@@ -10928,11 +10928,11 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -10948,11 +10948,11 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500">
@@ -10968,11 +10968,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D501" t="n">
@@ -11008,11 +11008,11 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -11023,16 +11023,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="504">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D504" t="n">
@@ -11068,11 +11068,11 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="506">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D506" t="n">
@@ -11108,11 +11108,11 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508">
@@ -11128,11 +11128,11 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="509">
@@ -11148,11 +11148,11 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -11163,16 +11163,16 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="511">
@@ -11188,11 +11188,11 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="512">
@@ -11208,11 +11208,11 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="513">
@@ -11228,11 +11228,11 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="514">
@@ -11248,11 +11248,11 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="515">
@@ -11268,11 +11268,11 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="516">
@@ -11288,11 +11288,11 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="517">
@@ -11308,11 +11308,11 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="518">
@@ -11323,16 +11323,16 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="519">
@@ -11348,11 +11348,11 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="520">
@@ -11368,11 +11368,11 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="521">
@@ -11388,11 +11388,11 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522">
@@ -11403,16 +11403,16 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="523">
@@ -11428,11 +11428,11 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="524">
@@ -11448,11 +11448,11 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="525">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D525" t="n">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="527">
@@ -11508,11 +11508,11 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="528">
@@ -11528,11 +11528,11 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="529">
@@ -11548,10 +11548,30 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D529" t="n">
+      <c r="D530" t="n">
         <v>11</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -507,16 +507,16 @@
         <v>54</v>
       </c>
       <c r="I2" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J2" t="n">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L2" t="n">
-        <v>5647</v>
+        <v>5643</v>
       </c>
     </row>
     <row r="3">
@@ -553,10 +553,10 @@
         <v>67</v>
       </c>
       <c r="K3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4">
@@ -569,7 +569,7 @@
         <v>347</v>
       </c>
       <c r="C4" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D4" t="n">
         <v>121</v>
@@ -596,7 +596,7 @@
         <v>33</v>
       </c>
       <c r="L4" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="5">
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C5" t="n">
         <v>340</v>
       </c>
       <c r="D5" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E5" t="n">
         <v>42</v>
@@ -636,7 +636,7 @@
         <v>62</v>
       </c>
       <c r="L5" t="n">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="6">
@@ -670,13 +670,13 @@
         <v>103</v>
       </c>
       <c r="J6" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K6" t="n">
         <v>49</v>
       </c>
       <c r="L6" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         <v>101</v>
       </c>
       <c r="C9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" t="n">
         <v>24</v>
@@ -796,7 +796,7 @@
         <v>15</v>
       </c>
       <c r="L9" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -889,7 +889,7 @@
         <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D12" t="n">
         <v>71</v>
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="L12" t="n">
-        <v>938</v>
+        <v>952</v>
       </c>
     </row>
     <row r="13">
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5354</v>
+        <v>5353</v>
       </c>
       <c r="C13" t="n">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="D13" t="n">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="E13" t="n">
         <v>294</v>
@@ -947,16 +947,16 @@
         <v>123</v>
       </c>
       <c r="I13" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="J13" t="n">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="K13" t="n">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="L13" t="n">
-        <v>13126</v>
+        <v>13130</v>
       </c>
     </row>
   </sheetData>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="54">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58">
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="90">
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="95">
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="97">
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115">
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="123">
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="162">
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="165">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="167">
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="205">
@@ -7652,7 +7652,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="367">
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="425">

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -873,10 +873,10 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
@@ -889,7 +889,7 @@
         <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D12" t="n">
         <v>71</v>
@@ -913,10 +913,10 @@
         <v>198</v>
       </c>
       <c r="K12" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L12" t="n">
-        <v>933</v>
+        <v>945</v>
       </c>
     </row>
     <row r="13">
@@ -929,7 +929,7 @@
         <v>5353</v>
       </c>
       <c r="C13" t="n">
-        <v>2665</v>
+        <v>2667</v>
       </c>
       <c r="D13" t="n">
         <v>1220</v>
@@ -953,10 +953,10 @@
         <v>1359</v>
       </c>
       <c r="K13" t="n">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="L13" t="n">
-        <v>13144</v>
+        <v>13157</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D528"/>
+  <dimension ref="A1:D529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47">
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="165">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="170">
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="199">
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="205">
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="242">
@@ -9848,11 +9848,11 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445">
@@ -9863,16 +9863,16 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="446">
@@ -9888,11 +9888,11 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="447">
@@ -9908,11 +9908,11 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D448" t="n">
@@ -9948,11 +9948,11 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D450" t="n">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D451" t="n">
@@ -10008,11 +10008,11 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -10028,31 +10028,31 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
@@ -10068,11 +10068,11 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="456">
@@ -10088,11 +10088,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="457">
@@ -10108,11 +10108,11 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -10128,11 +10128,11 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="459">
@@ -10148,11 +10148,11 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="460">
@@ -10168,11 +10168,11 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="461">
@@ -10188,11 +10188,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="462">
@@ -10208,11 +10208,11 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>115</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -10223,16 +10223,16 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>4</v>
+        <v>115</v>
       </c>
     </row>
     <row r="464">
@@ -10248,11 +10248,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="465">
@@ -10268,11 +10268,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="466">
@@ -10288,11 +10288,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="467">
@@ -10308,11 +10308,11 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D468" t="n">
@@ -10348,11 +10348,11 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="470">
@@ -10368,11 +10368,11 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="471">
@@ -10383,16 +10383,16 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="472">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D472" t="n">
@@ -10428,11 +10428,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="474">
@@ -10448,11 +10448,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D476" t="n">
@@ -10508,11 +10508,11 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="478">
@@ -10523,16 +10523,16 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="479">
@@ -10548,11 +10548,11 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="480">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -10588,11 +10588,11 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="482">
@@ -10608,11 +10608,11 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D483" t="n">
@@ -10648,11 +10648,11 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="485">
@@ -10668,11 +10668,11 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="486">
@@ -10688,11 +10688,11 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="487">
@@ -10708,11 +10708,11 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488">
@@ -10723,16 +10723,16 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="489">
@@ -10748,11 +10748,11 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="490">
@@ -10768,11 +10768,11 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="491">
@@ -10788,11 +10788,11 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="492">
@@ -10808,11 +10808,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="493">
@@ -10828,11 +10828,11 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -10848,11 +10848,11 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="495">
@@ -10868,11 +10868,11 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="496">
@@ -10888,11 +10888,11 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="497">
@@ -10903,16 +10903,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="498">
@@ -10928,11 +10928,11 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D499" t="n">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D500" t="n">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D501" t="n">
@@ -11008,11 +11008,11 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D503" t="n">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D504" t="n">
@@ -11068,11 +11068,11 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="506">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D506" t="n">
@@ -11108,11 +11108,11 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508">
@@ -11128,11 +11128,11 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="509">
@@ -11148,11 +11148,11 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -11163,16 +11163,16 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="511">
@@ -11188,11 +11188,11 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="512">
@@ -11208,11 +11208,11 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="513">
@@ -11228,11 +11228,11 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="514">
@@ -11248,11 +11248,11 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="515">
@@ -11268,11 +11268,11 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="516">
@@ -11288,11 +11288,11 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="517">
@@ -11308,11 +11308,11 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="518">
@@ -11323,16 +11323,16 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="519">
@@ -11348,11 +11348,11 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="520">
@@ -11368,11 +11368,11 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="521">
@@ -11388,11 +11388,11 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522">
@@ -11403,16 +11403,16 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="523">
@@ -11428,11 +11428,11 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="524">
@@ -11448,11 +11448,11 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="525">
@@ -11468,11 +11468,11 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="526">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="527">
@@ -11508,11 +11508,11 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="528">
@@ -11528,10 +11528,30 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D528" t="n">
+      <c r="D529" t="n">
         <v>11</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -510,13 +510,13 @@
         <v>314</v>
       </c>
       <c r="J2" t="n">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K2" t="n">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="L2" t="n">
-        <v>5657</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="3">
@@ -633,10 +633,10 @@
         <v>143</v>
       </c>
       <c r="K5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L5" t="n">
-        <v>1390</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="6">
@@ -713,10 +713,10 @@
         <v>202</v>
       </c>
       <c r="K7" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L7" t="n">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="8">
@@ -910,13 +910,13 @@
         <v>103</v>
       </c>
       <c r="J12" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L12" t="n">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="13">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57">
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="97">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="168">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="170">
@@ -4512,7 +4512,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178">
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="180">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="207">
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="309">
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="318">

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="L12" t="n">
-        <v>948</v>
+        <v>959</v>
       </c>
     </row>
     <row r="13">
@@ -953,10 +953,10 @@
         <v>1359</v>
       </c>
       <c r="K13" t="n">
-        <v>666</v>
+        <v>677</v>
       </c>
       <c r="L13" t="n">
-        <v>13157</v>
+        <v>13168</v>
       </c>
     </row>
   </sheetData>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="170">
